--- a/training/training_log.xlsx
+++ b/training/training_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Work\Data analysis in Python\ML_paper1\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Work\Data analysis in Python\ML_paper1\imputation-research\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C44C193-D559-4FD3-959A-11890AA8D616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A7BD22-E519-496B-AC87-7EC5AD00286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{67663D26-D449-4C21-9C49-EF5664B29A7E}"/>
+    <workbookView xWindow="38280" yWindow="2505" windowWidth="29040" windowHeight="15840" xr2:uid="{67663D26-D449-4C21-9C49-EF5664B29A7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="12">
   <si>
     <t>5 min</t>
   </si>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -251,35 +251,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,12 +666,12 @@
       <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -733,8 +739,8 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="17" t="s">
+      <c r="H4" s="20"/>
+      <c r="I4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="1"/>
@@ -767,10 +773,10 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="17" t="s">
+      <c r="H5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="1"/>
@@ -820,12 +826,12 @@
       <c r="V6" s="1"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
     </row>
     <row r="10" spans="1:22" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -848,32 +854,36 @@
       <c r="B11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
+      <c r="C11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
     </row>
     <row r="17" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -893,25 +903,25 @@
       <c r="A18" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
